--- a/Relatorio_Apostas_Completo_premier.xlsx
+++ b/Relatorio_Apostas_Completo_premier.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="34">
   <si>
     <t>Data_Hora</t>
   </si>
@@ -49,12 +49,6 @@
     <t>Lucro/Prejuízo</t>
   </si>
   <si>
-    <t>Tottenham</t>
-  </si>
-  <si>
-    <t>Wolverhampton</t>
-  </si>
-  <si>
     <t>Leicester</t>
   </si>
   <si>
@@ -70,6 +64,9 @@
     <t>Brighton</t>
   </si>
   <si>
+    <t>Wolverhampton</t>
+  </si>
+  <si>
     <t>Brentford</t>
   </si>
   <si>
@@ -82,16 +79,22 @@
     <t>Fulham</t>
   </si>
   <si>
-    <t>Everton</t>
+    <t>Aston Villa</t>
   </si>
   <si>
-    <t>Aston Villa</t>
+    <t>Everton</t>
   </si>
   <si>
     <t>Manchester City</t>
   </si>
   <si>
     <t>Manchester Utd</t>
+  </si>
+  <si>
+    <t>Bournemouth</t>
+  </si>
+  <si>
+    <t>Tottenham</t>
   </si>
   <si>
     <t>Newcastle</t>
@@ -103,13 +106,10 @@
     <t>Burnley</t>
   </si>
   <si>
-    <t>Bournemouth</t>
+    <t>Chelsea</t>
   </si>
   <si>
     <t>Leeds</t>
-  </si>
-  <si>
-    <t>Chelsea</t>
   </si>
   <si>
     <t>Liverpool</t>
@@ -477,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K126"/>
+  <dimension ref="A1:K122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -517,34 +517,34 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2">
-        <v>45648.5625</v>
+        <v>45655.47916666666</v>
       </c>
       <c r="B2" t="s">
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>4.75</v>
+        <v>9.5</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>6.03</v>
       </c>
       <c r="H2">
-        <v>21.05</v>
+        <v>10.53</v>
       </c>
       <c r="I2">
-        <v>33.35</v>
+        <v>16.58</v>
       </c>
       <c r="J2">
-        <v>58.4</v>
+        <v>57.51</v>
       </c>
       <c r="K2">
         <v>-1</v>
@@ -552,69 +552,69 @@
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="2">
-        <v>45652.60416666666</v>
+        <v>45655.59375</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>4.33</v>
+        <v>7</v>
       </c>
       <c r="G3">
-        <v>3.1</v>
+        <v>4.48</v>
       </c>
       <c r="H3">
-        <v>23.09</v>
+        <v>14.29</v>
       </c>
       <c r="I3">
-        <v>32.22</v>
+        <v>22.34</v>
       </c>
       <c r="J3">
-        <v>39.5</v>
+        <v>56.39</v>
       </c>
       <c r="K3">
-        <v>3.33</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="2">
-        <v>45655.47916666666</v>
+        <v>45661.5</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="G4">
-        <v>5.98</v>
+        <v>2.81</v>
       </c>
       <c r="H4">
-        <v>10.53</v>
+        <v>27.78</v>
       </c>
       <c r="I4">
-        <v>16.71</v>
+        <v>35.64</v>
       </c>
       <c r="J4">
-        <v>58.73</v>
+        <v>28.3</v>
       </c>
       <c r="K4">
         <v>-1</v>
@@ -622,13 +622,13 @@
     </row>
     <row r="5" spans="1:11">
       <c r="A5" s="2">
-        <v>45655.59375</v>
+        <v>45661.5</v>
       </c>
       <c r="B5" t="s">
         <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -637,19 +637,19 @@
         <v>5</v>
       </c>
       <c r="F5">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="G5">
-        <v>5.15</v>
+        <v>2.67</v>
       </c>
       <c r="H5">
-        <v>14.29</v>
+        <v>30.77</v>
       </c>
       <c r="I5">
-        <v>19.43</v>
+        <v>37.5</v>
       </c>
       <c r="J5">
-        <v>36.03</v>
+        <v>21.89</v>
       </c>
       <c r="K5">
         <v>-1</v>
@@ -657,13 +657,13 @@
     </row>
     <row r="6" spans="1:11">
       <c r="A6" s="2">
-        <v>45661.5</v>
+        <v>45661.60416666666</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -672,19 +672,19 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="H6">
-        <v>27.78</v>
+        <v>20</v>
       </c>
       <c r="I6">
-        <v>35.76</v>
+        <v>32.7</v>
       </c>
       <c r="J6">
-        <v>28.75</v>
+        <v>63.48</v>
       </c>
       <c r="K6">
         <v>-1</v>
@@ -692,7 +692,7 @@
     </row>
     <row r="7" spans="1:11">
       <c r="A7" s="2">
-        <v>45661.5</v>
+        <v>45663.70833333334</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
@@ -704,22 +704,22 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="G7">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="H7">
-        <v>30.77</v>
+        <v>25.64</v>
       </c>
       <c r="I7">
-        <v>39.04</v>
+        <v>34.71</v>
       </c>
       <c r="J7">
-        <v>26.87</v>
+        <v>35.36</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -727,34 +727,34 @@
     </row>
     <row r="8" spans="1:11">
       <c r="A8" s="2">
-        <v>45661.60416666666</v>
+        <v>45671.6875</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="G8">
-        <v>3.24</v>
+        <v>3.79</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="I8">
-        <v>30.84</v>
+        <v>26.39</v>
       </c>
       <c r="J8">
-        <v>54.2</v>
+        <v>38.54</v>
       </c>
       <c r="K8">
         <v>-1</v>
@@ -762,34 +762,34 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2">
-        <v>45663.70833333334</v>
+        <v>45671.70833333334</v>
       </c>
       <c r="B9" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>3.9</v>
+        <v>5.25</v>
       </c>
       <c r="G9">
-        <v>2.63</v>
+        <v>3.59</v>
       </c>
       <c r="H9">
-        <v>25.64</v>
+        <v>19.05</v>
       </c>
       <c r="I9">
-        <v>38</v>
+        <v>27.86</v>
       </c>
       <c r="J9">
-        <v>48.2</v>
+        <v>46.28</v>
       </c>
       <c r="K9">
         <v>-1</v>
@@ -797,34 +797,34 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" s="2">
-        <v>45671.6875</v>
+        <v>45676.5625</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F10">
-        <v>5.25</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>3.66</v>
+        <v>4.33</v>
       </c>
       <c r="H10">
-        <v>19.05</v>
+        <v>14.29</v>
       </c>
       <c r="I10">
-        <v>27.29</v>
+        <v>23.07</v>
       </c>
       <c r="J10">
-        <v>43.29</v>
+        <v>61.49</v>
       </c>
       <c r="K10">
         <v>-1</v>
@@ -832,34 +832,34 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" s="2">
-        <v>45671.70833333334</v>
+        <v>45682.5</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F11">
-        <v>5.25</v>
+        <v>6.5</v>
       </c>
       <c r="G11">
-        <v>3.54</v>
+        <v>4.91</v>
       </c>
       <c r="H11">
-        <v>19.05</v>
+        <v>15.38</v>
       </c>
       <c r="I11">
-        <v>28.28</v>
+        <v>20.35</v>
       </c>
       <c r="J11">
-        <v>48.45</v>
+        <v>32.25</v>
       </c>
       <c r="K11">
         <v>-1</v>
@@ -867,34 +867,34 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" s="2">
-        <v>45676.5625</v>
+        <v>45682.5</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="G12">
-        <v>3.76</v>
+        <v>3.62</v>
       </c>
       <c r="H12">
-        <v>14.29</v>
+        <v>17.39</v>
       </c>
       <c r="I12">
-        <v>26.56</v>
+        <v>27.63</v>
       </c>
       <c r="J12">
-        <v>85.93000000000001</v>
+        <v>58.85</v>
       </c>
       <c r="K12">
         <v>-1</v>
@@ -902,13 +902,13 @@
     </row>
     <row r="13" spans="1:11">
       <c r="A13" s="2">
-        <v>45682.5</v>
+        <v>45683.66666666666</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -917,19 +917,19 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="G13">
-        <v>3.91</v>
+        <v>1.65</v>
       </c>
       <c r="H13">
-        <v>17.39</v>
+        <v>42.55</v>
       </c>
       <c r="I13">
-        <v>25.59</v>
+        <v>60.43</v>
       </c>
       <c r="J13">
-        <v>47.15</v>
+        <v>42</v>
       </c>
       <c r="K13">
         <v>-1</v>
@@ -937,34 +937,34 @@
     </row>
     <row r="14" spans="1:11">
       <c r="A14" s="2">
-        <v>45682.5</v>
+        <v>45703.39583333334</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F14">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="G14">
-        <v>5.26</v>
+        <v>4.49</v>
       </c>
       <c r="H14">
-        <v>15.38</v>
+        <v>10.53</v>
       </c>
       <c r="I14">
-        <v>19.01</v>
+        <v>22.27</v>
       </c>
       <c r="J14">
-        <v>23.56</v>
+        <v>111.53</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -972,34 +972,34 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" s="2">
-        <v>45683.66666666666</v>
+        <v>45703.5</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
         <v>25</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15">
-        <v>2.35</v>
+        <v>6.25</v>
       </c>
       <c r="G15">
-        <v>1.76</v>
+        <v>4.35</v>
       </c>
       <c r="H15">
-        <v>42.55</v>
+        <v>16</v>
       </c>
       <c r="I15">
-        <v>56.7</v>
+        <v>23</v>
       </c>
       <c r="J15">
-        <v>33.25</v>
+        <v>43.74</v>
       </c>
       <c r="K15">
         <v>-1</v>
@@ -1007,10 +1007,10 @@
     </row>
     <row r="16" spans="1:11">
       <c r="A16" s="2">
-        <v>45700.6875</v>
+        <v>45707.6875</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s">
         <v>32</v>
@@ -1022,19 +1022,19 @@
         <v>2</v>
       </c>
       <c r="F16">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="G16">
-        <v>5.13</v>
+        <v>2.47</v>
       </c>
       <c r="H16">
-        <v>14.29</v>
+        <v>26.67</v>
       </c>
       <c r="I16">
-        <v>19.48</v>
+        <v>40.48</v>
       </c>
       <c r="J16">
-        <v>36.33</v>
+        <v>51.79</v>
       </c>
       <c r="K16">
         <v>-1</v>
@@ -1042,34 +1042,34 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" s="2">
-        <v>45703.39583333334</v>
+        <v>45710.39583333334</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E17">
         <v>2</v>
       </c>
       <c r="F17">
-        <v>9.5</v>
+        <v>2.63</v>
       </c>
       <c r="G17">
-        <v>4.84</v>
+        <v>2.01</v>
       </c>
       <c r="H17">
-        <v>10.53</v>
+        <v>38.02</v>
       </c>
       <c r="I17">
-        <v>20.67</v>
+        <v>49.7</v>
       </c>
       <c r="J17">
-        <v>96.34</v>
+        <v>30.7</v>
       </c>
       <c r="K17">
         <v>-1</v>
@@ -1077,34 +1077,34 @@
     </row>
     <row r="18" spans="1:11">
       <c r="A18" s="2">
-        <v>45703.5</v>
+        <v>45710.5</v>
       </c>
       <c r="B18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F18">
-        <v>6.25</v>
+        <v>2.1</v>
       </c>
       <c r="G18">
-        <v>4.42</v>
+        <v>1.62</v>
       </c>
       <c r="H18">
-        <v>16</v>
+        <v>47.62</v>
       </c>
       <c r="I18">
-        <v>22.61</v>
+        <v>61.55</v>
       </c>
       <c r="J18">
-        <v>41.3</v>
+        <v>29.26</v>
       </c>
       <c r="K18">
         <v>-1</v>
@@ -1112,34 +1112,34 @@
     </row>
     <row r="19" spans="1:11">
       <c r="A19" s="2">
-        <v>45707.6875</v>
+        <v>45710.5</v>
       </c>
       <c r="B19" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F19">
-        <v>3.75</v>
+        <v>5.25</v>
       </c>
       <c r="G19">
-        <v>2.41</v>
+        <v>3.8</v>
       </c>
       <c r="H19">
-        <v>26.67</v>
+        <v>19.05</v>
       </c>
       <c r="I19">
-        <v>41.51</v>
+        <v>26.31</v>
       </c>
       <c r="J19">
-        <v>55.67</v>
+        <v>38.12</v>
       </c>
       <c r="K19">
         <v>-1</v>
@@ -1147,34 +1147,34 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" s="2">
-        <v>45710.39583333334</v>
+        <v>45711.5625</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20">
         <v>2</v>
       </c>
       <c r="F20">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="G20">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="H20">
-        <v>38.02</v>
+        <v>33.33</v>
       </c>
       <c r="I20">
-        <v>54.87</v>
+        <v>53.6</v>
       </c>
       <c r="J20">
-        <v>44.31</v>
+        <v>60.81</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -1182,69 +1182,69 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" s="2">
-        <v>45710.5</v>
+        <v>45724.39583333334</v>
       </c>
       <c r="B21" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E21">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>5.25</v>
+        <v>3.8</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="H21">
-        <v>19.05</v>
+        <v>26.32</v>
       </c>
       <c r="I21">
-        <v>25</v>
+        <v>31.49</v>
       </c>
       <c r="J21">
-        <v>31.26</v>
+        <v>19.67</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="22" spans="1:11">
       <c r="A22" s="2">
-        <v>45710.5</v>
+        <v>45724.60416666666</v>
       </c>
       <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
         <v>21</v>
       </c>
-      <c r="C22" t="s">
-        <v>15</v>
-      </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="G22">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H22">
-        <v>47.62</v>
+        <v>46.51</v>
       </c>
       <c r="I22">
-        <v>58.27</v>
+        <v>57.31</v>
       </c>
       <c r="J22">
-        <v>22.36</v>
+        <v>23.22</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -1252,34 +1252,34 @@
     </row>
     <row r="23" spans="1:11">
       <c r="A23" s="2">
-        <v>45711.5625</v>
+        <v>45724.70833333334</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C23" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="G23">
-        <v>1.87</v>
+        <v>2.01</v>
       </c>
       <c r="H23">
-        <v>33.33</v>
+        <v>35.71</v>
       </c>
       <c r="I23">
-        <v>53.39</v>
+        <v>49.64</v>
       </c>
       <c r="J23">
-        <v>60.17</v>
+        <v>38.98</v>
       </c>
       <c r="K23">
         <v>-1</v>
@@ -1287,13 +1287,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" s="2">
-        <v>45724.60416666666</v>
+        <v>45726.70833333334</v>
       </c>
       <c r="B24" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -1302,19 +1302,19 @@
         <v>1</v>
       </c>
       <c r="F24">
-        <v>2.15</v>
+        <v>3.3</v>
       </c>
       <c r="G24">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="H24">
-        <v>46.51</v>
+        <v>30.3</v>
       </c>
       <c r="I24">
-        <v>60.68</v>
+        <v>42.87</v>
       </c>
       <c r="J24">
-        <v>30.47</v>
+        <v>41.46</v>
       </c>
       <c r="K24">
         <v>-1</v>
@@ -1322,34 +1322,34 @@
     </row>
     <row r="25" spans="1:11">
       <c r="A25" s="2">
-        <v>45724.70833333334</v>
+        <v>45731.5</v>
       </c>
       <c r="B25" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F25">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
       <c r="G25">
-        <v>2.15</v>
+        <v>2.63</v>
       </c>
       <c r="H25">
-        <v>35.71</v>
+        <v>25.64</v>
       </c>
       <c r="I25">
-        <v>46.48</v>
+        <v>37.98</v>
       </c>
       <c r="J25">
-        <v>30.15</v>
+        <v>48.12</v>
       </c>
       <c r="K25">
         <v>-1</v>
@@ -1357,34 +1357,34 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2">
-        <v>45726.70833333334</v>
+        <v>45732.66666666666</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="G26">
-        <v>2.2</v>
+        <v>3.6</v>
       </c>
       <c r="H26">
-        <v>30.3</v>
+        <v>22.22</v>
       </c>
       <c r="I26">
-        <v>45.45</v>
+        <v>27.78</v>
       </c>
       <c r="J26">
-        <v>49.99</v>
+        <v>25.01</v>
       </c>
       <c r="K26">
         <v>-1</v>
@@ -1392,34 +1392,34 @@
     </row>
     <row r="27" spans="1:11">
       <c r="A27" s="2">
-        <v>45731.5</v>
+        <v>45749.65625</v>
       </c>
       <c r="B27" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27">
-        <v>3.9</v>
+        <v>2.3</v>
       </c>
       <c r="G27">
-        <v>2.99</v>
+        <v>1.5</v>
       </c>
       <c r="H27">
-        <v>25.64</v>
+        <v>43.48</v>
       </c>
       <c r="I27">
-        <v>33.4</v>
+        <v>66.81</v>
       </c>
       <c r="J27">
-        <v>30.28</v>
+        <v>53.67</v>
       </c>
       <c r="K27">
         <v>-1</v>
@@ -1427,45 +1427,45 @@
     </row>
     <row r="28" spans="1:11">
       <c r="A28" s="2">
-        <v>45732.66666666666</v>
+        <v>45752.45833333334</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
       </c>
       <c r="C28" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E28">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="G28">
-        <v>3.41</v>
+        <v>2.11</v>
       </c>
       <c r="H28">
-        <v>22.22</v>
+        <v>40</v>
       </c>
       <c r="I28">
-        <v>29.3</v>
+        <v>47.43</v>
       </c>
       <c r="J28">
-        <v>31.86</v>
+        <v>18.58</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="29" spans="1:11">
       <c r="A29" s="2">
-        <v>45749.65625</v>
+        <v>45753.52083333334</v>
       </c>
       <c r="B29" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C29" t="s">
         <v>23</v>
@@ -1474,22 +1474,22 @@
         <v>0</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="G29">
-        <v>1.48</v>
+        <v>2.21</v>
       </c>
       <c r="H29">
-        <v>43.48</v>
+        <v>29.41</v>
       </c>
       <c r="I29">
-        <v>67.44</v>
+        <v>45.28</v>
       </c>
       <c r="J29">
-        <v>55.12</v>
+        <v>53.94</v>
       </c>
       <c r="K29">
         <v>-1</v>
@@ -1497,34 +1497,34 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2">
-        <v>45752.35416666666</v>
+        <v>45754.66666666666</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="C30" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>3.9</v>
+        <v>6.5</v>
       </c>
       <c r="G30">
-        <v>2.98</v>
+        <v>4.41</v>
       </c>
       <c r="H30">
-        <v>25.64</v>
+        <v>15.38</v>
       </c>
       <c r="I30">
-        <v>33.53</v>
+        <v>22.69</v>
       </c>
       <c r="J30">
-        <v>30.77</v>
+        <v>47.51</v>
       </c>
       <c r="K30">
         <v>-1</v>
@@ -1532,34 +1532,34 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="2">
-        <v>45753.52083333334</v>
+        <v>45759.45833333334</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F31">
-        <v>3.4</v>
+        <v>6.25</v>
       </c>
       <c r="G31">
-        <v>2.19</v>
+        <v>3.32</v>
       </c>
       <c r="H31">
-        <v>29.41</v>
+        <v>16</v>
       </c>
       <c r="I31">
-        <v>45.59</v>
+        <v>30.11</v>
       </c>
       <c r="J31">
-        <v>54.99</v>
+        <v>88.18000000000001</v>
       </c>
       <c r="K31">
         <v>-1</v>
@@ -1567,69 +1567,69 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="2">
-        <v>45754.66666666666</v>
+        <v>45761.66666666666</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>6.5</v>
+        <v>2.2</v>
       </c>
       <c r="G32">
-        <v>4.32</v>
+        <v>1.71</v>
       </c>
       <c r="H32">
-        <v>15.38</v>
+        <v>45.45</v>
       </c>
       <c r="I32">
-        <v>23.17</v>
+        <v>58.65</v>
       </c>
       <c r="J32">
-        <v>50.63</v>
+        <v>29.03</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="33" spans="1:11">
       <c r="A33" s="2">
-        <v>45759.45833333334</v>
+        <v>45767.41666666666</v>
       </c>
       <c r="B33" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33">
-        <v>6.25</v>
+        <v>9.5</v>
       </c>
       <c r="G33">
-        <v>3.26</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H33">
-        <v>16</v>
+        <v>10.53</v>
       </c>
       <c r="I33">
-        <v>30.7</v>
+        <v>12.44</v>
       </c>
       <c r="J33">
-        <v>91.88</v>
+        <v>18.17</v>
       </c>
       <c r="K33">
         <v>-1</v>
@@ -1637,69 +1637,69 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2">
-        <v>45760.41666666666</v>
+        <v>45773.45833333334</v>
       </c>
       <c r="B34" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C34" t="s">
         <v>11</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>2.2</v>
+        <v>1.53</v>
       </c>
       <c r="G34">
-        <v>1.87</v>
+        <v>1.28</v>
       </c>
       <c r="H34">
-        <v>45.45</v>
+        <v>65.36</v>
       </c>
       <c r="I34">
-        <v>53.41</v>
+        <v>78.42</v>
       </c>
       <c r="J34">
-        <v>17.5</v>
+        <v>19.98</v>
       </c>
       <c r="K34">
-        <v>1.2</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2">
-        <v>45767.41666666666</v>
+        <v>45773.45833333334</v>
       </c>
       <c r="B35" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
         <v>20</v>
       </c>
-      <c r="C35" t="s">
-        <v>33</v>
-      </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F35">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="G35">
-        <v>7.6</v>
+        <v>2.43</v>
       </c>
       <c r="H35">
-        <v>10.53</v>
+        <v>20</v>
       </c>
       <c r="I35">
-        <v>13.16</v>
+        <v>41.19</v>
       </c>
       <c r="J35">
-        <v>24.98</v>
+        <v>105.93</v>
       </c>
       <c r="K35">
         <v>-1</v>
@@ -1707,34 +1707,34 @@
     </row>
     <row r="36" spans="1:11">
       <c r="A36" s="2">
-        <v>45767.52083333334</v>
+        <v>45787.45833333334</v>
       </c>
       <c r="B36" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D36">
+        <v>0</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+      <c r="F36">
         <v>13</v>
       </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="D36">
-        <v>0</v>
-      </c>
-      <c r="E36">
-        <v>1</v>
-      </c>
-      <c r="F36">
-        <v>10</v>
-      </c>
       <c r="G36">
-        <v>7.79</v>
+        <v>6.79</v>
       </c>
       <c r="H36">
-        <v>10</v>
+        <v>7.69</v>
       </c>
       <c r="I36">
-        <v>12.84</v>
+        <v>14.72</v>
       </c>
       <c r="J36">
-        <v>28.38</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="K36">
         <v>-1</v>
@@ -1742,69 +1742,69 @@
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="2">
-        <v>45773.45833333334</v>
+        <v>45787.45833333334</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>1.53</v>
+        <v>2.9</v>
       </c>
       <c r="G37">
-        <v>1.26</v>
+        <v>1.67</v>
       </c>
       <c r="H37">
-        <v>65.36</v>
+        <v>34.48</v>
       </c>
       <c r="I37">
-        <v>79.11</v>
+        <v>59.92</v>
       </c>
       <c r="J37">
-        <v>21.04</v>
+        <v>73.77</v>
       </c>
       <c r="K37">
-        <v>0.53</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="38" spans="1:11">
       <c r="A38" s="2">
-        <v>45773.45833333334</v>
+        <v>45788.42708333334</v>
       </c>
       <c r="B38" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="G38">
-        <v>2.56</v>
+        <v>2.02</v>
       </c>
       <c r="H38">
-        <v>20</v>
+        <v>32.26</v>
       </c>
       <c r="I38">
-        <v>39.02</v>
+        <v>49.62</v>
       </c>
       <c r="J38">
-        <v>95.12</v>
+        <v>53.84</v>
       </c>
       <c r="K38">
         <v>-1</v>
@@ -1812,34 +1812,34 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2">
-        <v>45787.45833333334</v>
+        <v>45795.42708333334</v>
       </c>
       <c r="B39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C39" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>13</v>
+        <v>2.9</v>
       </c>
       <c r="G39">
-        <v>6.42</v>
+        <v>2.35</v>
       </c>
       <c r="H39">
-        <v>7.69</v>
+        <v>34.48</v>
       </c>
       <c r="I39">
-        <v>15.57</v>
+        <v>42.48</v>
       </c>
       <c r="J39">
-        <v>102.4</v>
+        <v>23.19</v>
       </c>
       <c r="K39">
         <v>-1</v>
@@ -1847,13 +1847,13 @@
     </row>
     <row r="40" spans="1:11">
       <c r="A40" s="2">
-        <v>45787.45833333334</v>
+        <v>45802.5</v>
       </c>
       <c r="B40" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C40" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -1862,19 +1862,19 @@
         <v>2</v>
       </c>
       <c r="F40">
-        <v>2.9</v>
+        <v>5.75</v>
       </c>
       <c r="G40">
-        <v>1.62</v>
+        <v>3.26</v>
       </c>
       <c r="H40">
-        <v>34.48</v>
+        <v>17.39</v>
       </c>
       <c r="I40">
-        <v>61.77</v>
+        <v>30.72</v>
       </c>
       <c r="J40">
-        <v>79.15000000000001</v>
+        <v>76.65000000000001</v>
       </c>
       <c r="K40">
         <v>-1</v>
@@ -1882,69 +1882,69 @@
     </row>
     <row r="41" spans="1:11">
       <c r="A41" s="2">
-        <v>45788.42708333334</v>
+        <v>45802.5</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="G41">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="H41">
-        <v>32.26</v>
+        <v>22.22</v>
       </c>
       <c r="I41">
-        <v>46.93</v>
+        <v>34.79</v>
       </c>
       <c r="J41">
-        <v>45.48</v>
+        <v>56.54</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2">
-        <v>45795.42708333334</v>
+        <v>45802.5</v>
       </c>
       <c r="B42" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D42">
         <v>1</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42">
         <v>2.9</v>
       </c>
       <c r="G42">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="H42">
         <v>34.48</v>
       </c>
       <c r="I42">
-        <v>41.94</v>
+        <v>44.52</v>
       </c>
       <c r="J42">
-        <v>21.63</v>
+        <v>29.12</v>
       </c>
       <c r="K42">
         <v>-1</v>
@@ -1955,31 +1955,31 @@
         <v>45802.5</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C43" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43">
         <v>2</v>
       </c>
       <c r="F43">
-        <v>5.75</v>
+        <v>12</v>
       </c>
       <c r="G43">
-        <v>3.52</v>
+        <v>5.68</v>
       </c>
       <c r="H43">
-        <v>17.39</v>
+        <v>8.33</v>
       </c>
       <c r="I43">
-        <v>28.42</v>
+        <v>17.61</v>
       </c>
       <c r="J43">
-        <v>63.43</v>
+        <v>111.31</v>
       </c>
       <c r="K43">
         <v>-1</v>
@@ -1987,34 +1987,34 @@
     </row>
     <row r="44" spans="1:11">
       <c r="A44" s="2">
-        <v>45802.5</v>
+        <v>45885.5625</v>
       </c>
       <c r="B44" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C44" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F44">
-        <v>2.9</v>
+        <v>6.25</v>
       </c>
       <c r="G44">
-        <v>2.36</v>
+        <v>3.41</v>
       </c>
       <c r="H44">
-        <v>34.48</v>
+        <v>16</v>
       </c>
       <c r="I44">
-        <v>42.3</v>
+        <v>29.34</v>
       </c>
       <c r="J44">
-        <v>22.68</v>
+        <v>83.39</v>
       </c>
       <c r="K44">
         <v>-1</v>
@@ -2022,34 +2022,34 @@
     </row>
     <row r="45" spans="1:11">
       <c r="A45" s="2">
-        <v>45802.5</v>
+        <v>45886.52083333334</v>
       </c>
       <c r="B45" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C45" t="s">
         <v>33</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45">
-        <v>12</v>
+        <v>3.8</v>
       </c>
       <c r="G45">
-        <v>4.81</v>
+        <v>2.04</v>
       </c>
       <c r="H45">
-        <v>8.33</v>
+        <v>26.32</v>
       </c>
       <c r="I45">
-        <v>20.79</v>
+        <v>49.03</v>
       </c>
       <c r="J45">
-        <v>149.44</v>
+        <v>86.33</v>
       </c>
       <c r="K45">
         <v>-1</v>
@@ -2057,69 +2057,69 @@
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="2">
-        <v>45802.5</v>
+        <v>45891.66666666666</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C46" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E46">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F46">
         <v>4.5</v>
       </c>
       <c r="G46">
-        <v>3.03</v>
+        <v>2.78</v>
       </c>
       <c r="H46">
         <v>22.22</v>
       </c>
       <c r="I46">
-        <v>33.01</v>
+        <v>35.94</v>
       </c>
       <c r="J46">
-        <v>48.54</v>
+        <v>61.71</v>
       </c>
       <c r="K46">
-        <v>3.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="47" spans="1:11">
       <c r="A47" s="2">
-        <v>45885.5625</v>
+        <v>45892.35416666666</v>
       </c>
       <c r="B47" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F47">
-        <v>6.25</v>
+        <v>1.55</v>
       </c>
       <c r="G47">
-        <v>3.66</v>
+        <v>1.25</v>
       </c>
       <c r="H47">
-        <v>16</v>
+        <v>64.52</v>
       </c>
       <c r="I47">
-        <v>27.29</v>
+        <v>80.18000000000001</v>
       </c>
       <c r="J47">
-        <v>70.59</v>
+        <v>24.29</v>
       </c>
       <c r="K47">
         <v>-1</v>
@@ -2127,69 +2127,69 @@
     </row>
     <row r="48" spans="1:11">
       <c r="A48" s="2">
-        <v>45886.52083333334</v>
+        <v>45892.45833333334</v>
       </c>
       <c r="B48" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="G48">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="H48">
-        <v>26.32</v>
+        <v>29.41</v>
       </c>
       <c r="I48">
-        <v>46.74</v>
+        <v>48.18</v>
       </c>
       <c r="J48">
-        <v>77.62</v>
+        <v>63.82</v>
       </c>
       <c r="K48">
-        <v>-1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="49" spans="1:11">
       <c r="A49" s="2">
-        <v>45891.66666666666</v>
+        <v>45894.66666666666</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F49">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="G49">
-        <v>2.74</v>
+        <v>1.79</v>
       </c>
       <c r="H49">
-        <v>22.22</v>
+        <v>34.48</v>
       </c>
       <c r="I49">
-        <v>36.43</v>
+        <v>55.92</v>
       </c>
       <c r="J49">
-        <v>63.93</v>
+        <v>62.16</v>
       </c>
       <c r="K49">
         <v>-1</v>
@@ -2197,124 +2197,124 @@
     </row>
     <row r="50" spans="1:11">
       <c r="A50" s="2">
-        <v>45892.35416666666</v>
+        <v>45899.45833333334</v>
       </c>
       <c r="B50" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="G50">
-        <v>1.27</v>
+        <v>1.86</v>
       </c>
       <c r="H50">
-        <v>64.52</v>
+        <v>32.26</v>
       </c>
       <c r="I50">
-        <v>78.52</v>
+        <v>53.65</v>
       </c>
       <c r="J50">
-        <v>21.7</v>
+        <v>66.31999999999999</v>
       </c>
       <c r="K50">
-        <v>-1</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="51" spans="1:11">
       <c r="A51" s="2">
-        <v>45892.45833333334</v>
+        <v>45899.45833333334</v>
       </c>
       <c r="B51" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F51">
         <v>3.4</v>
       </c>
       <c r="G51">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="H51">
         <v>29.41</v>
       </c>
       <c r="I51">
-        <v>48.68</v>
+        <v>38.44</v>
       </c>
       <c r="J51">
-        <v>65.51000000000001</v>
+        <v>30.68</v>
       </c>
       <c r="K51">
-        <v>2.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="52" spans="1:11">
       <c r="A52" s="2">
-        <v>45894.66666666666</v>
+        <v>45900.41666666666</v>
       </c>
       <c r="B52" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C52" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D52">
         <v>2</v>
       </c>
       <c r="E52">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F52">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="G52">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="H52">
-        <v>34.48</v>
+        <v>27.78</v>
       </c>
       <c r="I52">
-        <v>52.24</v>
+        <v>44.89</v>
       </c>
       <c r="J52">
-        <v>51.51</v>
+        <v>61.61</v>
       </c>
       <c r="K52">
-        <v>-1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="53" spans="1:11">
       <c r="A53" s="2">
-        <v>45899.45833333334</v>
+        <v>45913.5625</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C53" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F53">
         <v>3.1</v>
@@ -2326,45 +2326,45 @@
         <v>32.26</v>
       </c>
       <c r="I53">
-        <v>57.45</v>
+        <v>57.31</v>
       </c>
       <c r="J53">
-        <v>78.09999999999999</v>
+        <v>77.66</v>
       </c>
       <c r="K53">
-        <v>2.1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="54" spans="1:11">
       <c r="A54" s="2">
-        <v>45899.45833333334</v>
+        <v>45914.41666666666</v>
       </c>
       <c r="B54" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="C54" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="G54">
-        <v>2.52</v>
+        <v>3.87</v>
       </c>
       <c r="H54">
-        <v>29.41</v>
+        <v>11.11</v>
       </c>
       <c r="I54">
-        <v>39.61</v>
+        <v>25.86</v>
       </c>
       <c r="J54">
-        <v>34.68</v>
+        <v>132.78</v>
       </c>
       <c r="K54">
         <v>-1</v>
@@ -2372,69 +2372,69 @@
     </row>
     <row r="55" spans="1:11">
       <c r="A55" s="2">
-        <v>45900.41666666666</v>
+        <v>45921.41666666666</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C55" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="G55">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="H55">
-        <v>27.78</v>
+        <v>40</v>
       </c>
       <c r="I55">
-        <v>46.13</v>
+        <v>51.4</v>
       </c>
       <c r="J55">
-        <v>66.05</v>
+        <v>28.5</v>
       </c>
       <c r="K55">
-        <v>2.6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="56" spans="1:11">
       <c r="A56" s="2">
-        <v>45913.45833333334</v>
+        <v>45921.41666666666</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="G56">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="H56">
-        <v>37.04</v>
+        <v>26.32</v>
       </c>
       <c r="I56">
-        <v>45.69</v>
+        <v>55.46</v>
       </c>
       <c r="J56">
-        <v>23.35</v>
+        <v>110.74</v>
       </c>
       <c r="K56">
         <v>-1</v>
@@ -2442,104 +2442,104 @@
     </row>
     <row r="57" spans="1:11">
       <c r="A57" s="2">
-        <v>45913.5625</v>
+        <v>45927.45833333334</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="G57">
-        <v>1.91</v>
+        <v>3.2</v>
       </c>
       <c r="H57">
-        <v>32.26</v>
+        <v>23.81</v>
       </c>
       <c r="I57">
-        <v>52.41</v>
+        <v>31.29</v>
       </c>
       <c r="J57">
-        <v>62.47</v>
+        <v>31.4</v>
       </c>
       <c r="K57">
-        <v>-1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="58" spans="1:11">
       <c r="A58" s="2">
-        <v>45914.41666666666</v>
+        <v>45934.5625</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C58" t="s">
         <v>32</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E58">
         <v>1</v>
       </c>
       <c r="F58">
-        <v>9</v>
+        <v>2.9</v>
       </c>
       <c r="G58">
-        <v>4</v>
+        <v>2.41</v>
       </c>
       <c r="H58">
-        <v>11.11</v>
+        <v>34.48</v>
       </c>
       <c r="I58">
-        <v>24.98</v>
+        <v>41.57</v>
       </c>
       <c r="J58">
-        <v>124.81</v>
+        <v>20.56</v>
       </c>
       <c r="K58">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="59" spans="1:11">
       <c r="A59" s="2">
-        <v>45920.45833333334</v>
+        <v>45935.41666666666</v>
       </c>
       <c r="B59" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F59">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="G59">
-        <v>2.63</v>
+        <v>2.44</v>
       </c>
       <c r="H59">
-        <v>32.26</v>
+        <v>29.41</v>
       </c>
       <c r="I59">
-        <v>37.97</v>
+        <v>40.99</v>
       </c>
       <c r="J59">
-        <v>17.71</v>
+        <v>39.36</v>
       </c>
       <c r="K59">
         <v>-1</v>
@@ -2547,34 +2547,34 @@
     </row>
     <row r="60" spans="1:11">
       <c r="A60" s="2">
-        <v>45921.41666666666</v>
+        <v>45935.52083333334</v>
       </c>
       <c r="B60" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="G60">
-        <v>1.85</v>
+        <v>3.44</v>
       </c>
       <c r="H60">
-        <v>40</v>
+        <v>21.05</v>
       </c>
       <c r="I60">
-        <v>54.07</v>
+        <v>29.08</v>
       </c>
       <c r="J60">
-        <v>35.16</v>
+        <v>38.11</v>
       </c>
       <c r="K60">
         <v>-1</v>
@@ -2582,188 +2582,188 @@
     </row>
     <row r="61" spans="1:11">
       <c r="A61" s="2">
-        <v>45921.41666666666</v>
+        <v>45948.45833333334</v>
       </c>
       <c r="B61" t="s">
+        <v>15</v>
+      </c>
+      <c r="C61" t="s">
         <v>27</v>
       </c>
-      <c r="C61" t="s">
-        <v>23</v>
-      </c>
       <c r="D61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61">
         <v>1</v>
       </c>
       <c r="F61">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="G61">
-        <v>1.75</v>
+        <v>2.09</v>
       </c>
       <c r="H61">
-        <v>26.32</v>
+        <v>34.72</v>
       </c>
       <c r="I61">
-        <v>57.12</v>
+        <v>47.77</v>
       </c>
       <c r="J61">
-        <v>117.05</v>
+        <v>37.58</v>
       </c>
       <c r="K61">
-        <v>-1</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="62" spans="1:11">
       <c r="A62" s="2">
-        <v>45927.45833333334</v>
+        <v>45948.5625</v>
       </c>
       <c r="B62" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E62">
         <v>1</v>
       </c>
       <c r="F62">
+        <v>6.25</v>
+      </c>
+      <c r="G62">
         <v>4.2</v>
       </c>
-      <c r="G62">
-        <v>3.17</v>
-      </c>
       <c r="H62">
-        <v>23.81</v>
+        <v>16</v>
       </c>
       <c r="I62">
-        <v>31.52</v>
+        <v>23.83</v>
       </c>
       <c r="J62">
-        <v>32.37</v>
+        <v>48.92</v>
       </c>
       <c r="K62">
-        <v>3.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="63" spans="1:11">
       <c r="A63" s="2">
-        <v>45935.41666666666</v>
+        <v>45954.66666666666</v>
       </c>
       <c r="B63" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" t="s">
         <v>12</v>
       </c>
-      <c r="C63" t="s">
-        <v>17</v>
-      </c>
       <c r="D63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="G63">
-        <v>2.4</v>
+        <v>1.34</v>
       </c>
       <c r="H63">
-        <v>29.41</v>
+        <v>55.56</v>
       </c>
       <c r="I63">
-        <v>41.62</v>
+        <v>74.70999999999999</v>
       </c>
       <c r="J63">
-        <v>41.5</v>
+        <v>34.47</v>
       </c>
       <c r="K63">
-        <v>-1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="64" spans="1:11">
       <c r="A64" s="2">
-        <v>45935.52083333334</v>
+        <v>45955.66666666666</v>
       </c>
       <c r="B64" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="G64">
-        <v>3.44</v>
+        <v>2.66</v>
       </c>
       <c r="H64">
-        <v>21.05</v>
+        <v>25.64</v>
       </c>
       <c r="I64">
-        <v>29.06</v>
+        <v>37.54</v>
       </c>
       <c r="J64">
-        <v>38.03</v>
+        <v>46.41</v>
       </c>
       <c r="K64">
-        <v>-1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="65" spans="1:11">
       <c r="A65" s="2">
-        <v>45948.45833333334</v>
+        <v>45962.5</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="C65" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65">
-        <v>2.88</v>
+        <v>13</v>
       </c>
       <c r="G65">
-        <v>1.98</v>
+        <v>7.29</v>
       </c>
       <c r="H65">
-        <v>34.72</v>
+        <v>7.69</v>
       </c>
       <c r="I65">
-        <v>50.39</v>
+        <v>13.71</v>
       </c>
       <c r="J65">
-        <v>45.11</v>
+        <v>78.22</v>
       </c>
       <c r="K65">
-        <v>1.88</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="66" spans="1:11">
       <c r="A66" s="2">
-        <v>45948.5625</v>
+        <v>45962.60416666666</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C66" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2772,19 +2772,19 @@
         <v>1</v>
       </c>
       <c r="F66">
-        <v>6.25</v>
+        <v>3.1</v>
       </c>
       <c r="G66">
-        <v>4.36</v>
+        <v>2.48</v>
       </c>
       <c r="H66">
-        <v>16</v>
+        <v>32.26</v>
       </c>
       <c r="I66">
-        <v>22.95</v>
+        <v>40.33</v>
       </c>
       <c r="J66">
-        <v>43.45</v>
+        <v>25.03</v>
       </c>
       <c r="K66">
         <v>-1</v>
@@ -2792,77 +2792,77 @@
     </row>
     <row r="67" spans="1:11">
       <c r="A67" s="2">
-        <v>45954.66666666666</v>
+        <v>45964.70833333334</v>
       </c>
       <c r="B67" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C67" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="G67">
-        <v>1.37</v>
+        <v>2.4</v>
       </c>
       <c r="H67">
-        <v>55.56</v>
+        <v>30.3</v>
       </c>
       <c r="I67">
-        <v>72.93000000000001</v>
+        <v>41.75</v>
       </c>
       <c r="J67">
-        <v>31.27</v>
+        <v>37.78</v>
       </c>
       <c r="K67">
-        <v>0.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68" spans="1:11">
       <c r="A68" s="2">
-        <v>45955.66666666666</v>
+        <v>45969.39583333334</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E68">
         <v>2</v>
       </c>
       <c r="F68">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="G68">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="H68">
-        <v>25.64</v>
+        <v>34.48</v>
       </c>
       <c r="I68">
-        <v>41.71</v>
+        <v>41.9</v>
       </c>
       <c r="J68">
-        <v>62.66</v>
+        <v>21.5</v>
       </c>
       <c r="K68">
-        <v>2.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="69" spans="1:11">
       <c r="A69" s="2">
-        <v>45962.5</v>
+        <v>45969.60416666666</v>
       </c>
       <c r="B69" t="s">
         <v>28</v>
@@ -2871,25 +2871,25 @@
         <v>33</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E69">
         <v>2</v>
       </c>
       <c r="F69">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="G69">
-        <v>6.12</v>
+        <v>5.2</v>
       </c>
       <c r="H69">
-        <v>7.69</v>
+        <v>13.33</v>
       </c>
       <c r="I69">
-        <v>16.35</v>
+        <v>19.24</v>
       </c>
       <c r="J69">
-        <v>112.51</v>
+        <v>44.29</v>
       </c>
       <c r="K69">
         <v>-1</v>
@@ -2897,104 +2897,104 @@
     </row>
     <row r="70" spans="1:11">
       <c r="A70" s="2">
-        <v>45962.60416666666</v>
+        <v>45970.45833333334</v>
       </c>
       <c r="B70" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E70">
         <v>1</v>
       </c>
       <c r="F70">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="G70">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="H70">
-        <v>32.26</v>
+        <v>35.71</v>
       </c>
       <c r="I70">
-        <v>40.97</v>
+        <v>49.24</v>
       </c>
       <c r="J70">
-        <v>26.99</v>
+        <v>37.87</v>
       </c>
       <c r="K70">
-        <v>-1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="71" spans="1:11">
       <c r="A71" s="2">
-        <v>45964.70833333334</v>
+        <v>45970.5625</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C71" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>3.3</v>
+        <v>1.85</v>
       </c>
       <c r="G71">
-        <v>2.27</v>
+        <v>1.51</v>
       </c>
       <c r="H71">
-        <v>30.3</v>
+        <v>54.05</v>
       </c>
       <c r="I71">
-        <v>44.05</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="J71">
-        <v>45.37</v>
+        <v>22.23</v>
       </c>
       <c r="K71">
-        <v>-1</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="2">
-        <v>45969.39583333334</v>
+        <v>45984.45833333334</v>
       </c>
       <c r="B72" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E72">
         <v>2</v>
       </c>
       <c r="F72">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G72">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="H72">
-        <v>34.48</v>
+        <v>31.25</v>
       </c>
       <c r="I72">
-        <v>45.43</v>
+        <v>40.01</v>
       </c>
       <c r="J72">
-        <v>31.74</v>
+        <v>28.02</v>
       </c>
       <c r="K72">
         <v>-1</v>
@@ -3002,174 +3002,174 @@
     </row>
     <row r="73" spans="1:11">
       <c r="A73" s="2">
-        <v>45969.60416666666</v>
+        <v>45990.5</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C73" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E73">
         <v>2</v>
       </c>
       <c r="F73">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="G73">
-        <v>4.43</v>
+        <v>2.7</v>
       </c>
       <c r="H73">
-        <v>13.33</v>
+        <v>31.25</v>
       </c>
       <c r="I73">
-        <v>22.56</v>
+        <v>37.06</v>
       </c>
       <c r="J73">
-        <v>69.16</v>
+        <v>18.59</v>
       </c>
       <c r="K73">
-        <v>-1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="74" spans="1:11">
       <c r="A74" s="2">
-        <v>45970.45833333334</v>
+        <v>45991.46180555555</v>
       </c>
       <c r="B74" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C74" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="G74">
-        <v>2.12</v>
+        <v>3.32</v>
       </c>
       <c r="H74">
-        <v>35.71</v>
+        <v>21.05</v>
       </c>
       <c r="I74">
-        <v>47.12</v>
+        <v>30.12</v>
       </c>
       <c r="J74">
-        <v>31.93</v>
+        <v>43.05</v>
       </c>
       <c r="K74">
-        <v>1.8</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="75" spans="1:11">
       <c r="A75" s="2">
-        <v>45970.45833333334</v>
+        <v>45991.5625</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="G75">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="H75">
-        <v>43.48</v>
+        <v>34.72</v>
       </c>
       <c r="I75">
-        <v>50.87</v>
+        <v>45.62</v>
       </c>
       <c r="J75">
-        <v>17.01</v>
+        <v>31.39</v>
       </c>
       <c r="K75">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="76" spans="1:11">
       <c r="A76" s="2">
-        <v>45970.5625</v>
+        <v>45993.6875</v>
       </c>
       <c r="B76" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C76" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F76">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="G76">
-        <v>1.57</v>
+        <v>2.78</v>
       </c>
       <c r="H76">
-        <v>54.05</v>
+        <v>20</v>
       </c>
       <c r="I76">
-        <v>63.85</v>
+        <v>35.99</v>
       </c>
       <c r="J76">
-        <v>18.12</v>
+        <v>79.95999999999999</v>
       </c>
       <c r="K76">
-        <v>0.85</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="77" spans="1:11">
       <c r="A77" s="2">
-        <v>45984.45833333334</v>
+        <v>45993.6875</v>
       </c>
       <c r="B77" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C77" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77">
-        <v>3.2</v>
+        <v>2.15</v>
       </c>
       <c r="G77">
-        <v>2.51</v>
+        <v>1.59</v>
       </c>
       <c r="H77">
-        <v>31.25</v>
+        <v>46.51</v>
       </c>
       <c r="I77">
-        <v>39.78</v>
+        <v>62.87</v>
       </c>
       <c r="J77">
-        <v>27.29</v>
+        <v>35.17</v>
       </c>
       <c r="K77">
         <v>-1</v>
@@ -3177,34 +3177,34 @@
     </row>
     <row r="78" spans="1:11">
       <c r="A78" s="2">
-        <v>45991.46180555555</v>
+        <v>45994.6875</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C78" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78">
         <v>4.75</v>
       </c>
       <c r="G78">
-        <v>3.11</v>
+        <v>3.42</v>
       </c>
       <c r="H78">
         <v>21.05</v>
       </c>
       <c r="I78">
-        <v>32.13</v>
+        <v>29.22</v>
       </c>
       <c r="J78">
-        <v>52.59</v>
+        <v>38.81</v>
       </c>
       <c r="K78">
         <v>-1</v>
@@ -3212,69 +3212,69 @@
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="2">
-        <v>45991.5625</v>
+        <v>45997.39583333334</v>
       </c>
       <c r="B79" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C79" t="s">
         <v>33</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79">
         <v>1</v>
       </c>
       <c r="F79">
-        <v>2.88</v>
+        <v>4.2</v>
       </c>
       <c r="G79">
-        <v>2.36</v>
+        <v>3.01</v>
       </c>
       <c r="H79">
-        <v>34.72</v>
+        <v>23.81</v>
       </c>
       <c r="I79">
-        <v>42.33</v>
+        <v>33.19</v>
       </c>
       <c r="J79">
-        <v>21.91</v>
+        <v>39.4</v>
       </c>
       <c r="K79">
-        <v>-1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="80" spans="1:11">
       <c r="A80" s="2">
-        <v>45993.6875</v>
+        <v>45997.60416666666</v>
       </c>
       <c r="B80" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C80" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="G80">
-        <v>1.74</v>
+        <v>3.52</v>
       </c>
       <c r="H80">
-        <v>46.51</v>
+        <v>23.81</v>
       </c>
       <c r="I80">
-        <v>57.53</v>
+        <v>28.41</v>
       </c>
       <c r="J80">
-        <v>23.69</v>
+        <v>19.32</v>
       </c>
       <c r="K80">
         <v>-1</v>
@@ -3282,34 +3282,34 @@
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="2">
-        <v>45993.6875</v>
+        <v>45998.5625</v>
       </c>
       <c r="B81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F81">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="G81">
-        <v>2.87</v>
+        <v>1.93</v>
       </c>
       <c r="H81">
-        <v>20</v>
+        <v>41.67</v>
       </c>
       <c r="I81">
-        <v>34.79</v>
+        <v>51.8</v>
       </c>
       <c r="J81">
-        <v>73.95999999999999</v>
+        <v>24.33</v>
       </c>
       <c r="K81">
         <v>-1</v>
@@ -3317,34 +3317,34 @@
     </row>
     <row r="82" spans="1:11">
       <c r="A82" s="2">
-        <v>45994.6875</v>
+        <v>46004.60416666666</v>
       </c>
       <c r="B82" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C82" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F82">
-        <v>4.75</v>
+        <v>3.9</v>
       </c>
       <c r="G82">
-        <v>3.4</v>
+        <v>3.01</v>
       </c>
       <c r="H82">
-        <v>21.05</v>
+        <v>25.64</v>
       </c>
       <c r="I82">
+        <v>33.19</v>
+      </c>
+      <c r="J82">
         <v>29.44</v>
-      </c>
-      <c r="J82">
-        <v>39.86</v>
       </c>
       <c r="K82">
         <v>-1</v>
@@ -3352,104 +3352,104 @@
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="2">
-        <v>45997.39583333334</v>
+        <v>46005.45833333334</v>
       </c>
       <c r="B83" t="s">
+        <v>13</v>
+      </c>
+      <c r="C83" t="s">
         <v>23</v>
       </c>
-      <c r="C83" t="s">
-        <v>33</v>
-      </c>
       <c r="D83">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="G83">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="H83">
-        <v>23.81</v>
+        <v>25</v>
       </c>
       <c r="I83">
-        <v>31.39</v>
+        <v>32.61</v>
       </c>
       <c r="J83">
-        <v>31.85</v>
+        <v>30.43</v>
       </c>
       <c r="K83">
-        <v>3.2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="2">
-        <v>45998.5625</v>
+        <v>46005.45833333334</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C84" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F84">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="G84">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="H84">
-        <v>41.67</v>
+        <v>37.04</v>
       </c>
       <c r="I84">
-        <v>50.29</v>
+        <v>49.51</v>
       </c>
       <c r="J84">
-        <v>20.69</v>
+        <v>33.67</v>
       </c>
       <c r="K84">
-        <v>-1</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="85" spans="1:11">
       <c r="A85" s="2">
-        <v>46004.60416666666</v>
+        <v>46011.39583333334</v>
       </c>
       <c r="B85" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D85">
         <v>2</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="G85">
-        <v>2.85</v>
+        <v>1.79</v>
       </c>
       <c r="H85">
-        <v>25.64</v>
+        <v>35.71</v>
       </c>
       <c r="I85">
-        <v>35.09</v>
+        <v>55.71</v>
       </c>
       <c r="J85">
-        <v>36.85</v>
+        <v>56</v>
       </c>
       <c r="K85">
         <v>-1</v>
@@ -3457,34 +3457,34 @@
     </row>
     <row r="86" spans="1:11">
       <c r="A86" s="2">
-        <v>46005.45833333334</v>
+        <v>46011.5</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="G86">
-        <v>3.25</v>
+        <v>1.57</v>
       </c>
       <c r="H86">
-        <v>25</v>
+        <v>54.05</v>
       </c>
       <c r="I86">
-        <v>30.73</v>
+        <v>63.86</v>
       </c>
       <c r="J86">
-        <v>22.93</v>
+        <v>18.15</v>
       </c>
       <c r="K86">
         <v>-1</v>
@@ -3492,174 +3492,174 @@
     </row>
     <row r="87" spans="1:11">
       <c r="A87" s="2">
-        <v>46005.45833333334</v>
+        <v>46011.70833333334</v>
       </c>
       <c r="B87" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C87" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F87">
-        <v>2.7</v>
+        <v>6.25</v>
       </c>
       <c r="G87">
-        <v>2.22</v>
+        <v>3.76</v>
       </c>
       <c r="H87">
-        <v>37.04</v>
+        <v>16</v>
       </c>
       <c r="I87">
-        <v>45.14</v>
+        <v>26.59</v>
       </c>
       <c r="J87">
-        <v>21.88</v>
+        <v>66.16</v>
       </c>
       <c r="K87">
-        <v>1.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="88" spans="1:11">
       <c r="A88" s="2">
-        <v>46011.39583333334</v>
+        <v>46011.70833333334</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C88" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="G88">
-        <v>1.78</v>
+        <v>2.28</v>
       </c>
       <c r="H88">
-        <v>35.71</v>
+        <v>34.72</v>
       </c>
       <c r="I88">
-        <v>56.21</v>
+        <v>43.83</v>
       </c>
       <c r="J88">
-        <v>57.4</v>
+        <v>26.22</v>
       </c>
       <c r="K88">
-        <v>-1</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="89" spans="1:11">
       <c r="A89" s="2">
-        <v>46011.5</v>
+        <v>46017.70833333334</v>
       </c>
       <c r="B89" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C89" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>3.4</v>
+        <v>2.5</v>
       </c>
       <c r="G89">
-        <v>2.68</v>
+        <v>1.89</v>
       </c>
       <c r="H89">
-        <v>29.41</v>
+        <v>40</v>
       </c>
       <c r="I89">
-        <v>37.33</v>
+        <v>52.83</v>
       </c>
       <c r="J89">
-        <v>26.92</v>
+        <v>32.07</v>
       </c>
       <c r="K89">
-        <v>-1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="90" spans="1:11">
       <c r="A90" s="2">
-        <v>46011.70833333334</v>
+        <v>46018.39583333334</v>
       </c>
       <c r="B90" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C90" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D90">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F90">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="G90">
-        <v>2.35</v>
+        <v>3.27</v>
       </c>
       <c r="H90">
-        <v>34.72</v>
+        <v>20</v>
       </c>
       <c r="I90">
-        <v>42.47</v>
+        <v>30.56</v>
       </c>
       <c r="J90">
-        <v>22.32</v>
+        <v>52.81</v>
       </c>
       <c r="K90">
-        <v>1.88</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="2">
-        <v>46011.70833333334</v>
+        <v>46018.5</v>
       </c>
       <c r="B91" t="s">
+        <v>29</v>
+      </c>
+      <c r="C91" t="s">
         <v>22</v>
       </c>
-      <c r="C91" t="s">
-        <v>33</v>
-      </c>
       <c r="D91">
         <v>0</v>
       </c>
       <c r="E91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F91">
-        <v>6.25</v>
+        <v>3.6</v>
       </c>
       <c r="G91">
-        <v>3.74</v>
+        <v>2.59</v>
       </c>
       <c r="H91">
-        <v>16</v>
+        <v>27.78</v>
       </c>
       <c r="I91">
-        <v>26.71</v>
+        <v>38.66</v>
       </c>
       <c r="J91">
-        <v>66.92</v>
+        <v>39.18</v>
       </c>
       <c r="K91">
         <v>-1</v>
@@ -3667,34 +3667,34 @@
     </row>
     <row r="92" spans="1:11">
       <c r="A92" s="2">
-        <v>46018.39583333334</v>
+        <v>46021.6875</v>
       </c>
       <c r="B92" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C92" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92">
         <v>2</v>
       </c>
       <c r="F92">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="G92">
-        <v>3.54</v>
+        <v>2.6</v>
       </c>
       <c r="H92">
-        <v>20</v>
+        <v>29.41</v>
       </c>
       <c r="I92">
-        <v>28.27</v>
+        <v>38.53</v>
       </c>
       <c r="J92">
-        <v>41.37</v>
+        <v>31</v>
       </c>
       <c r="K92">
         <v>-1</v>
@@ -3702,34 +3702,34 @@
     </row>
     <row r="93" spans="1:11">
       <c r="A93" s="2">
-        <v>46018.5</v>
+        <v>46021.6875</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C93" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F93">
-        <v>3.6</v>
+        <v>5.5</v>
       </c>
       <c r="G93">
-        <v>2.42</v>
+        <v>3.03</v>
       </c>
       <c r="H93">
-        <v>27.78</v>
+        <v>18.18</v>
       </c>
       <c r="I93">
-        <v>41.25</v>
+        <v>32.99</v>
       </c>
       <c r="J93">
-        <v>48.5</v>
+        <v>81.45</v>
       </c>
       <c r="K93">
         <v>-1</v>
@@ -3737,34 +3737,34 @@
     </row>
     <row r="94" spans="1:11">
       <c r="A94" s="2">
-        <v>46021.6875</v>
+        <v>46023.70833333334</v>
       </c>
       <c r="B94" t="s">
         <v>28</v>
       </c>
       <c r="C94" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F94">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="G94">
-        <v>2.81</v>
+        <v>5.43</v>
       </c>
       <c r="H94">
-        <v>18.18</v>
+        <v>14.29</v>
       </c>
       <c r="I94">
-        <v>35.61</v>
+        <v>18.41</v>
       </c>
       <c r="J94">
-        <v>95.84</v>
+        <v>28.87</v>
       </c>
       <c r="K94">
         <v>-1</v>
@@ -3772,34 +3772,34 @@
     </row>
     <row r="95" spans="1:11">
       <c r="A95" s="2">
-        <v>46021.6875</v>
+        <v>46025.60416666666</v>
       </c>
       <c r="B95" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D95">
         <v>2</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F95">
-        <v>3.4</v>
+        <v>6</v>
       </c>
       <c r="G95">
-        <v>2.36</v>
+        <v>3.49</v>
       </c>
       <c r="H95">
-        <v>29.41</v>
+        <v>16.67</v>
       </c>
       <c r="I95">
-        <v>42.45</v>
+        <v>28.64</v>
       </c>
       <c r="J95">
-        <v>44.33</v>
+        <v>71.83</v>
       </c>
       <c r="K95">
         <v>-1</v>
@@ -3807,34 +3807,34 @@
     </row>
     <row r="96" spans="1:11">
       <c r="A96" s="2">
-        <v>46023.70833333334</v>
+        <v>46026.51041666666</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C96" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F96">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G96">
-        <v>5.1</v>
+        <v>2.68</v>
       </c>
       <c r="H96">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="I96">
-        <v>19.61</v>
+        <v>37.37</v>
       </c>
       <c r="J96">
-        <v>37.3</v>
+        <v>49.49</v>
       </c>
       <c r="K96">
         <v>-1</v>
@@ -3842,69 +3842,69 @@
     </row>
     <row r="97" spans="1:11">
       <c r="A97" s="2">
-        <v>46025.60416666666</v>
+        <v>46029.6875</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C97" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D97">
         <v>2</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F97">
-        <v>6</v>
+        <v>3.7</v>
       </c>
       <c r="G97">
-        <v>4.13</v>
+        <v>2.02</v>
       </c>
       <c r="H97">
-        <v>16.67</v>
+        <v>27.03</v>
       </c>
       <c r="I97">
-        <v>24.2</v>
+        <v>49.56</v>
       </c>
       <c r="J97">
-        <v>45.2</v>
+        <v>83.37</v>
       </c>
       <c r="K97">
-        <v>-1</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="98" spans="1:11">
       <c r="A98" s="2">
-        <v>46026.39583333334</v>
+        <v>46029.71875</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C98" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F98">
-        <v>2.8</v>
+        <v>4.75</v>
       </c>
       <c r="G98">
-        <v>2.24</v>
+        <v>3.29</v>
       </c>
       <c r="H98">
-        <v>35.71</v>
+        <v>21.05</v>
       </c>
       <c r="I98">
-        <v>44.65</v>
+        <v>30.4</v>
       </c>
       <c r="J98">
-        <v>25.02</v>
+        <v>44.39</v>
       </c>
       <c r="K98">
         <v>-1</v>
@@ -3912,34 +3912,34 @@
     </row>
     <row r="99" spans="1:11">
       <c r="A99" s="2">
-        <v>46026.51041666666</v>
+        <v>46039.60416666666</v>
       </c>
       <c r="B99" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C99" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F99">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="G99">
-        <v>2.56</v>
+        <v>3.47</v>
       </c>
       <c r="H99">
-        <v>25</v>
+        <v>18.18</v>
       </c>
       <c r="I99">
-        <v>38.99</v>
+        <v>28.79</v>
       </c>
       <c r="J99">
-        <v>55.96</v>
+        <v>58.35</v>
       </c>
       <c r="K99">
         <v>-1</v>
@@ -3947,69 +3947,69 @@
     </row>
     <row r="100" spans="1:11">
       <c r="A100" s="2">
-        <v>46029.6875</v>
+        <v>46040.45833333334</v>
       </c>
       <c r="B100" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C100" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="G100">
-        <v>1.99</v>
+        <v>2.81</v>
       </c>
       <c r="H100">
-        <v>27.03</v>
+        <v>22.22</v>
       </c>
       <c r="I100">
-        <v>50.21</v>
+        <v>35.55</v>
       </c>
       <c r="J100">
-        <v>85.77</v>
+        <v>59.98</v>
       </c>
       <c r="K100">
-        <v>2.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="101" spans="1:11">
       <c r="A101" s="2">
-        <v>46029.71875</v>
+        <v>46047.45833333334</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="G101">
-        <v>3</v>
+        <v>2.59</v>
       </c>
       <c r="H101">
-        <v>21.05</v>
+        <v>29.41</v>
       </c>
       <c r="I101">
-        <v>33.33</v>
+        <v>38.56</v>
       </c>
       <c r="J101">
-        <v>58.3</v>
+        <v>31.1</v>
       </c>
       <c r="K101">
         <v>-1</v>
@@ -4017,34 +4017,34 @@
     </row>
     <row r="102" spans="1:11">
       <c r="A102" s="2">
-        <v>46039.60416666666</v>
+        <v>46053.5</v>
       </c>
       <c r="B102" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D102">
         <v>0</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102">
-        <v>5.5</v>
+        <v>2.8</v>
       </c>
       <c r="G102">
-        <v>3.48</v>
+        <v>2.12</v>
       </c>
       <c r="H102">
-        <v>18.18</v>
+        <v>35.71</v>
       </c>
       <c r="I102">
-        <v>28.74</v>
+        <v>47.06</v>
       </c>
       <c r="J102">
-        <v>58.06</v>
+        <v>31.77</v>
       </c>
       <c r="K102">
         <v>-1</v>
@@ -4052,34 +4052,34 @@
     </row>
     <row r="103" spans="1:11">
       <c r="A103" s="2">
-        <v>46040.45833333334</v>
+        <v>46053.5</v>
       </c>
       <c r="B103" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C103" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>0</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F103">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="G103">
-        <v>2.74</v>
+        <v>3.31</v>
       </c>
       <c r="H103">
-        <v>22.22</v>
+        <v>18.18</v>
       </c>
       <c r="I103">
-        <v>36.49</v>
+        <v>30.19</v>
       </c>
       <c r="J103">
-        <v>64.2</v>
+        <v>66.03</v>
       </c>
       <c r="K103">
         <v>-1</v>
@@ -4087,34 +4087,34 @@
     </row>
     <row r="104" spans="1:11">
       <c r="A104" s="2">
-        <v>46047.45833333334</v>
+        <v>46054.5625</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C104" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F104">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="G104">
-        <v>2.34</v>
+        <v>2.19</v>
       </c>
       <c r="H104">
-        <v>29.41</v>
+        <v>21.05</v>
       </c>
       <c r="I104">
-        <v>42.71</v>
+        <v>45.68</v>
       </c>
       <c r="J104">
-        <v>45.21</v>
+        <v>116.98</v>
       </c>
       <c r="K104">
         <v>-1</v>
@@ -4122,69 +4122,69 @@
     </row>
     <row r="105" spans="1:11">
       <c r="A105" s="2">
-        <v>46053.5</v>
+        <v>46055.70833333334</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C105" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E105">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F105">
-        <v>5.5</v>
+        <v>1.91</v>
       </c>
       <c r="G105">
-        <v>3.52</v>
+        <v>1.52</v>
       </c>
       <c r="H105">
-        <v>18.18</v>
+        <v>52.36</v>
       </c>
       <c r="I105">
-        <v>28.37</v>
+        <v>65.95</v>
       </c>
       <c r="J105">
-        <v>56.05</v>
+        <v>25.97</v>
       </c>
       <c r="K105">
-        <v>-1</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="106" spans="1:11">
       <c r="A106" s="2">
-        <v>46053.5</v>
+        <v>46060.5</v>
       </c>
       <c r="B106" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="G106">
-        <v>1.99</v>
+        <v>2.12</v>
       </c>
       <c r="H106">
-        <v>35.71</v>
+        <v>20</v>
       </c>
       <c r="I106">
-        <v>50.29</v>
+        <v>47.07</v>
       </c>
       <c r="J106">
-        <v>40.82</v>
+        <v>135.36</v>
       </c>
       <c r="K106">
         <v>-1</v>
@@ -4192,34 +4192,34 @@
     </row>
     <row r="107" spans="1:11">
       <c r="A107" s="2">
-        <v>46054.5625</v>
+        <v>46061.5625</v>
       </c>
       <c r="B107" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C107" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E107">
         <v>2</v>
       </c>
       <c r="F107">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="G107">
-        <v>2.41</v>
+        <v>1.73</v>
       </c>
       <c r="H107">
-        <v>21.05</v>
+        <v>47.62</v>
       </c>
       <c r="I107">
-        <v>41.51</v>
+        <v>57.81</v>
       </c>
       <c r="J107">
-        <v>97.15000000000001</v>
+        <v>21.41</v>
       </c>
       <c r="K107">
         <v>-1</v>
@@ -4227,69 +4227,69 @@
     </row>
     <row r="108" spans="1:11">
       <c r="A108" s="2">
-        <v>46055.70833333334</v>
+        <v>46063.6875</v>
       </c>
       <c r="B108" t="s">
+        <v>26</v>
+      </c>
+      <c r="C108" t="s">
         <v>27</v>
       </c>
-      <c r="C108" t="s">
-        <v>28</v>
-      </c>
       <c r="D108">
+        <v>1</v>
+      </c>
+      <c r="E108">
+        <v>2</v>
+      </c>
+      <c r="F108">
         <v>3</v>
       </c>
-      <c r="E108">
-        <v>0</v>
-      </c>
-      <c r="F108">
-        <v>1.91</v>
-      </c>
       <c r="G108">
-        <v>1.46</v>
+        <v>2.33</v>
       </c>
       <c r="H108">
-        <v>52.36</v>
+        <v>33.33</v>
       </c>
       <c r="I108">
-        <v>68.58</v>
+        <v>43</v>
       </c>
       <c r="J108">
-        <v>30.98</v>
+        <v>29.01</v>
       </c>
       <c r="K108">
-        <v>0.91</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="109" spans="1:11">
       <c r="A109" s="2">
-        <v>46060.5</v>
+        <v>46063.71875</v>
       </c>
       <c r="B109" t="s">
         <v>12</v>
       </c>
       <c r="C109" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D109">
         <v>1</v>
       </c>
       <c r="E109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109">
-        <v>5</v>
+        <v>4.33</v>
       </c>
       <c r="G109">
-        <v>2.09</v>
+        <v>3.49</v>
       </c>
       <c r="H109">
-        <v>20</v>
+        <v>23.09</v>
       </c>
       <c r="I109">
-        <v>47.93</v>
+        <v>28.67</v>
       </c>
       <c r="J109">
-        <v>139.67</v>
+        <v>24.15</v>
       </c>
       <c r="K109">
         <v>-1</v>
@@ -4297,34 +4297,34 @@
     </row>
     <row r="110" spans="1:11">
       <c r="A110" s="2">
-        <v>46063.6875</v>
+        <v>46064.71875</v>
       </c>
       <c r="B110" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C110" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="G110">
-        <v>2.44</v>
+        <v>3.42</v>
       </c>
       <c r="H110">
-        <v>33.33</v>
+        <v>23.09</v>
       </c>
       <c r="I110">
-        <v>40.96</v>
+        <v>29.27</v>
       </c>
       <c r="J110">
-        <v>22.87</v>
+        <v>26.75</v>
       </c>
       <c r="K110">
         <v>-1</v>
@@ -4332,13 +4332,13 @@
     </row>
     <row r="111" spans="1:11">
       <c r="A111" s="2">
-        <v>46063.71875</v>
+        <v>46065.70833333334</v>
       </c>
       <c r="B111" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C111" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -4347,19 +4347,19 @@
         <v>1</v>
       </c>
       <c r="F111">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="G111">
-        <v>3.28</v>
+        <v>4.11</v>
       </c>
       <c r="H111">
-        <v>23.09</v>
+        <v>20</v>
       </c>
       <c r="I111">
-        <v>30.48</v>
+        <v>24.33</v>
       </c>
       <c r="J111">
-        <v>31.96</v>
+        <v>21.66</v>
       </c>
       <c r="K111">
         <v>-1</v>
@@ -4367,34 +4367,34 @@
     </row>
     <row r="112" spans="1:11">
       <c r="A112" s="2">
-        <v>46064.71875</v>
+        <v>46071.70833333334</v>
       </c>
       <c r="B112" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C112" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112">
-        <v>4.33</v>
+        <v>12</v>
       </c>
       <c r="G112">
-        <v>3.07</v>
+        <v>6.08</v>
       </c>
       <c r="H112">
-        <v>23.09</v>
+        <v>8.33</v>
       </c>
       <c r="I112">
-        <v>32.6</v>
+        <v>16.45</v>
       </c>
       <c r="J112">
-        <v>41.18</v>
+        <v>97.37</v>
       </c>
       <c r="K112">
         <v>-1</v>
@@ -4402,34 +4402,34 @@
     </row>
     <row r="113" spans="1:11">
       <c r="A113" s="2">
-        <v>46065.70833333334</v>
+        <v>46075.45833333334</v>
       </c>
       <c r="B113" t="s">
         <v>18</v>
       </c>
       <c r="C113" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E113">
         <v>1</v>
       </c>
       <c r="F113">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="G113">
-        <v>4.21</v>
+        <v>2.66</v>
       </c>
       <c r="H113">
-        <v>20</v>
+        <v>27.78</v>
       </c>
       <c r="I113">
-        <v>23.74</v>
+        <v>37.61</v>
       </c>
       <c r="J113">
-        <v>18.68</v>
+        <v>35.41</v>
       </c>
       <c r="K113">
         <v>-1</v>
@@ -4437,34 +4437,34 @@
     </row>
     <row r="114" spans="1:11">
       <c r="A114" s="2">
-        <v>46071.70833333334</v>
+        <v>46075.45833333334</v>
       </c>
       <c r="B114" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C114" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="D114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114">
-        <v>12</v>
+        <v>2.88</v>
       </c>
       <c r="G114">
-        <v>6.04</v>
+        <v>2.21</v>
       </c>
       <c r="H114">
-        <v>8.33</v>
+        <v>34.72</v>
       </c>
       <c r="I114">
-        <v>16.56</v>
+        <v>45.31</v>
       </c>
       <c r="J114">
-        <v>98.66</v>
+        <v>30.49</v>
       </c>
       <c r="K114">
         <v>-1</v>
@@ -4472,34 +4472,34 @@
     </row>
     <row r="115" spans="1:11">
       <c r="A115" s="2">
-        <v>46075.45833333334</v>
+        <v>46075.5625</v>
       </c>
       <c r="B115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C115" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>1</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F115">
-        <v>2.88</v>
+        <v>7.5</v>
       </c>
       <c r="G115">
-        <v>2.18</v>
+        <v>4.26</v>
       </c>
       <c r="H115">
-        <v>34.72</v>
+        <v>13.33</v>
       </c>
       <c r="I115">
-        <v>45.92</v>
+        <v>23.49</v>
       </c>
       <c r="J115">
-        <v>32.25</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="K115">
         <v>-1</v>
@@ -4507,48 +4507,48 @@
     </row>
     <row r="116" spans="1:11">
       <c r="A116" s="2">
-        <v>46075.45833333334</v>
+        <v>46081.5</v>
       </c>
       <c r="B116" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C116" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F116">
-        <v>1.75</v>
+        <v>4.33</v>
       </c>
       <c r="G116">
-        <v>1.44</v>
+        <v>2.6</v>
       </c>
       <c r="H116">
-        <v>57.14</v>
+        <v>23.09</v>
       </c>
       <c r="I116">
-        <v>69.37</v>
+        <v>38.49</v>
       </c>
       <c r="J116">
-        <v>21.4</v>
+        <v>66.66</v>
       </c>
       <c r="K116">
-        <v>0.75</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="117" spans="1:11">
       <c r="A117" s="2">
-        <v>46075.45833333334</v>
+        <v>46081.60416666666</v>
       </c>
       <c r="B117" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C117" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -4557,19 +4557,19 @@
         <v>1</v>
       </c>
       <c r="F117">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="G117">
-        <v>2.7</v>
+        <v>3.59</v>
       </c>
       <c r="H117">
-        <v>27.78</v>
+        <v>21.05</v>
       </c>
       <c r="I117">
-        <v>37</v>
+        <v>27.83</v>
       </c>
       <c r="J117">
-        <v>33.19</v>
+        <v>32.18</v>
       </c>
       <c r="K117">
         <v>-1</v>
@@ -4577,104 +4577,104 @@
     </row>
     <row r="118" spans="1:11">
       <c r="A118" s="2">
-        <v>46075.5625</v>
+        <v>46082.45833333334</v>
       </c>
       <c r="B118" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C118" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F118">
-        <v>7.5</v>
+        <v>2.05</v>
       </c>
       <c r="G118">
-        <v>4.63</v>
+        <v>1.6</v>
       </c>
       <c r="H118">
-        <v>13.33</v>
+        <v>48.78</v>
       </c>
       <c r="I118">
-        <v>21.58</v>
+        <v>62.63</v>
       </c>
       <c r="J118">
-        <v>61.85</v>
+        <v>28.39</v>
       </c>
       <c r="K118">
-        <v>-1</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="119" spans="1:11">
       <c r="A119" s="2">
-        <v>46080.70833333334</v>
+        <v>46084.71875</v>
       </c>
       <c r="B119" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="D119">
         <v>2</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119">
-        <v>4.75</v>
+        <v>6.5</v>
       </c>
       <c r="G119">
-        <v>3.42</v>
+        <v>4.93</v>
       </c>
       <c r="H119">
-        <v>21.05</v>
+        <v>15.38</v>
       </c>
       <c r="I119">
-        <v>29.25</v>
+        <v>20.29</v>
       </c>
       <c r="J119">
-        <v>38.96</v>
+        <v>31.86</v>
       </c>
       <c r="K119">
-        <v>3.75</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="120" spans="1:11">
       <c r="A120" s="2">
-        <v>46081.5</v>
+        <v>46085.6875</v>
       </c>
       <c r="B120" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C120" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="D120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F120">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="G120">
-        <v>2.65</v>
+        <v>3.53</v>
       </c>
       <c r="H120">
-        <v>23.09</v>
+        <v>20</v>
       </c>
       <c r="I120">
-        <v>37.8</v>
+        <v>28.3</v>
       </c>
       <c r="J120">
-        <v>63.66</v>
+        <v>41.52</v>
       </c>
       <c r="K120">
         <v>-1</v>
@@ -4682,16 +4682,16 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="2">
-        <v>46081.60416666666</v>
+        <v>46095.70833333334</v>
       </c>
       <c r="B121" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C121" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4700,16 +4700,16 @@
         <v>4.75</v>
       </c>
       <c r="G121">
-        <v>3.55</v>
+        <v>3.06</v>
       </c>
       <c r="H121">
         <v>21.05</v>
       </c>
       <c r="I121">
-        <v>28.13</v>
+        <v>32.64</v>
       </c>
       <c r="J121">
-        <v>33.63</v>
+        <v>55.06</v>
       </c>
       <c r="K121">
         <v>-1</v>
@@ -4717,176 +4717,36 @@
     </row>
     <row r="122" spans="1:11">
       <c r="A122" s="2">
-        <v>46082.45833333334</v>
+        <v>46101.70833333334</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C122" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="D122">
         <v>2</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F122">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="G122">
-        <v>1.56</v>
+        <v>2.51</v>
       </c>
       <c r="H122">
-        <v>48.78</v>
+        <v>32.26</v>
       </c>
       <c r="I122">
-        <v>64.08</v>
+        <v>39.91</v>
       </c>
       <c r="J122">
-        <v>31.36</v>
+        <v>23.73</v>
       </c>
       <c r="K122">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" s="2">
-        <v>46084.71875</v>
-      </c>
-      <c r="B123" t="s">
-        <v>12</v>
-      </c>
-      <c r="C123" t="s">
-        <v>32</v>
-      </c>
-      <c r="D123">
-        <v>2</v>
-      </c>
-      <c r="E123">
-        <v>1</v>
-      </c>
-      <c r="F123">
-        <v>6.5</v>
-      </c>
-      <c r="G123">
-        <v>4.5</v>
-      </c>
-      <c r="H123">
-        <v>15.38</v>
-      </c>
-      <c r="I123">
-        <v>22.2</v>
-      </c>
-      <c r="J123">
-        <v>44.3</v>
-      </c>
-      <c r="K123">
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
-      <c r="A124" s="2">
-        <v>46085.6875</v>
-      </c>
-      <c r="B124" t="s">
-        <v>17</v>
-      </c>
-      <c r="C124" t="s">
-        <v>33</v>
-      </c>
-      <c r="D124">
-        <v>0</v>
-      </c>
-      <c r="E124">
-        <v>1</v>
-      </c>
-      <c r="F124">
-        <v>5</v>
-      </c>
-      <c r="G124">
-        <v>3.61</v>
-      </c>
-      <c r="H124">
-        <v>20</v>
-      </c>
-      <c r="I124">
-        <v>27.68</v>
-      </c>
-      <c r="J124">
-        <v>38.41</v>
-      </c>
-      <c r="K124">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" s="2">
-        <v>46095.5</v>
-      </c>
-      <c r="B125" t="s">
-        <v>28</v>
-      </c>
-      <c r="C125" t="s">
-        <v>29</v>
-      </c>
-      <c r="D125">
-        <v>0</v>
-      </c>
-      <c r="E125">
-        <v>0</v>
-      </c>
-      <c r="F125">
-        <v>3.9</v>
-      </c>
-      <c r="G125">
-        <v>3.2</v>
-      </c>
-      <c r="H125">
-        <v>25.64</v>
-      </c>
-      <c r="I125">
-        <v>31.2</v>
-      </c>
-      <c r="J125">
-        <v>21.7</v>
-      </c>
-      <c r="K125">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" s="2">
-        <v>46095.70833333334</v>
-      </c>
-      <c r="B126" t="s">
-        <v>14</v>
-      </c>
-      <c r="C126" t="s">
-        <v>24</v>
-      </c>
-      <c r="D126">
-        <v>1</v>
-      </c>
-      <c r="E126">
-        <v>1</v>
-      </c>
-      <c r="F126">
-        <v>4.75</v>
-      </c>
-      <c r="G126">
-        <v>3.16</v>
-      </c>
-      <c r="H126">
-        <v>21.05</v>
-      </c>
-      <c r="I126">
-        <v>31.63</v>
-      </c>
-      <c r="J126">
-        <v>50.26</v>
-      </c>
-      <c r="K126">
         <v>-1</v>
       </c>
     </row>
